--- a/artfynd/S 1552-2025 artfynd.xlsx
+++ b/artfynd/S 1552-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,55 +887,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128391165</v>
+        <v>135546480</v>
       </c>
       <c r="B4" t="n">
-        <v>89098</v>
+        <v>58134</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4388</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mönjevaxing</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrocybe miniata</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sextondelen, Sm</t>
+          <t>Knäred-Traryd, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412263</v>
+        <v>411630</v>
       </c>
       <c r="R4" t="n">
-        <v>6265462</v>
+        <v>6266258</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,22 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,17 +989,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ieva Mardega, Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132465798</v>
+        <v>135546465</v>
       </c>
       <c r="B5" t="n">
-        <v>97862</v>
+        <v>57162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,41 +1007,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2606</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sextondelen, Sm</t>
+          <t>Knäred-Traryd, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412460</v>
+        <v>411918</v>
       </c>
       <c r="R5" t="n">
-        <v>6265290</v>
+        <v>6265583</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1073,19 +1076,14 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:53</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vårvinter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,10 +1110,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132465691</v>
+        <v>128391165</v>
       </c>
       <c r="B6" t="n">
-        <v>96501</v>
+        <v>89098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,41 +1121,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>4388</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Mönjevaxing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hygrocybe miniata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) P.Kumm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillån, Sm</t>
+          <t>Sextondelen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412446</v>
+        <v>412263</v>
       </c>
       <c r="R6" t="n">
-        <v>6265274</v>
+        <v>6265462</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1181,22 +1182,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,17 +1217,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Ieva Mardega, Louise Lindroth</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132466032</v>
+        <v>135546478</v>
       </c>
       <c r="B7" t="n">
-        <v>81036</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1234,40 +1235,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230185</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sextondelen, Sm</t>
+          <t>Knäred-Traryd, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412459</v>
+        <v>412259</v>
       </c>
       <c r="R7" t="n">
-        <v>6265340</v>
+        <v>6265503</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1294,19 +1301,9 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,6 +1327,449 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132465798</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97862</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sextondelen, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>412460</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6265290</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hinneryd</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132465691</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96501</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lillån, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>412446</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6265274</v>
+      </c>
+      <c r="S9" t="n">
+        <v>9</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hinneryd</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135546364</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Knäred-Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>412314</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6265245</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132466032</v>
+      </c>
+      <c r="B11" t="n">
+        <v>81036</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sextondelen, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>412459</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6265340</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hinneryd</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 1552-2025 artfynd.xlsx
+++ b/artfynd/S 1552-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/696609</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Skogsstyrelsens naturvärdesobjekt</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/669676</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135546480</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135546465</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1221,6 +1246,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128391165</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1327,6 +1357,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135546478</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1438,6 +1473,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132465798</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1549,6 +1589,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132465691</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1660,6 +1705,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135546364</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1770,8 +1820,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132466032</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 1552-2025 artfynd.xlsx
+++ b/artfynd/S 1552-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>135546480</v>
       </c>
       <c r="B4" t="n">
-        <v>58134</v>
+        <v>58139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135546465</v>
       </c>
       <c r="B5" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>135546478</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>135546364</v>
       </c>
       <c r="B10" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/S 1552-2025 artfynd.xlsx
+++ b/artfynd/S 1552-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,55 +902,60 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128391165</v>
+        <v>135546480</v>
       </c>
       <c r="B4" t="n">
-        <v>89098</v>
+        <v>58139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4388</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mönjevaxing</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrocybe miniata</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) P.Kumm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sextondelen, Sm</t>
+          <t>Knäred-Traryd, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412263</v>
+        <v>411630</v>
       </c>
       <c r="R4" t="n">
-        <v>6265462</v>
+        <v>6266258</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,22 +979,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1004,22 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ieva Mardega, Louise Lindroth</t>
+          <t>Ieva Mardega</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128391165</t>
+          <t>https://artportalen.se/Sighting/135546480</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132465798</v>
+        <v>135546465</v>
       </c>
       <c r="B5" t="n">
-        <v>97862</v>
+        <v>57167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,41 +1027,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2606</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sextondelen, Sm</t>
+          <t>Knäred-Traryd, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412460</v>
+        <v>411918</v>
       </c>
       <c r="R5" t="n">
-        <v>6265290</v>
+        <v>6265583</v>
       </c>
       <c r="S5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,19 +1096,14 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:53</t>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Vårvinter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,16 +1129,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132465798</t>
+          <t>https://artportalen.se/Sighting/135546465</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132465691</v>
+        <v>128391165</v>
       </c>
       <c r="B6" t="n">
-        <v>96501</v>
+        <v>89098</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1148,41 +1146,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2671</v>
+        <v>4388</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Mönjevaxing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hygrocybe miniata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Fr.) P.Kumm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lillån, Sm</t>
+          <t>Sextondelen, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>412446</v>
+        <v>412263</v>
       </c>
       <c r="R6" t="n">
-        <v>6265274</v>
+        <v>6265462</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,22 +1207,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,22 +1242,22 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Ieva Mardega</t>
+          <t>Ieva Mardega, Louise Lindroth</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132465691</t>
+          <t>https://artportalen.se/Sighting/128391165</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132466032</v>
+        <v>135546478</v>
       </c>
       <c r="B7" t="n">
-        <v>81036</v>
+        <v>57977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,40 +1265,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230185</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sextondelen, Sm</t>
+          <t>Knäred-Traryd, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>412459</v>
+        <v>412259</v>
       </c>
       <c r="R7" t="n">
-        <v>6265340</v>
+        <v>6265503</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,19 +1331,9 @@
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,6 +1358,469 @@
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135546478</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132465798</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97862</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2606</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Klippfrullania</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sextondelen, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>412460</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6265290</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hinneryd</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132465798</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132465691</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96501</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lillån, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>412446</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6265274</v>
+      </c>
+      <c r="S9" t="n">
+        <v>9</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hinneryd</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132465691</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135546364</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57167</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Knäred-Traryd, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>412314</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6265245</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Fjäder</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135546364</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132466032</v>
+      </c>
+      <c r="B11" t="n">
+        <v>81036</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sextondelen, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>412459</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6265340</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hinneryd</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132466032</t>
         </is>
@@ -1374,6 +1834,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1552-2025 artfynd.xlsx
+++ b/artfynd/S 1552-2025 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>135546480</v>
       </c>
       <c r="B4" t="n">
-        <v>58139</v>
+        <v>58141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135546465</v>
       </c>
       <c r="B5" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
         <v>135546478</v>
       </c>
       <c r="B7" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1600,7 +1600,7 @@
         <v>135546364</v>
       </c>
       <c r="B10" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
